--- a/demo-data/statement.xlsx
+++ b/demo-data/statement.xlsx
@@ -48,9 +48,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E301"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,6 +446,11 @@
           <t>Currency</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -452,16 +458,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GETT TAXI 811441</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>108.47</v>
-      </c>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>12450.3</v>
       </c>
     </row>
     <row r="3">
@@ -470,17 +478,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KSP COMPUTERS</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>194.25</v>
-      </c>
+          <t>GETT TAXI 811441</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>108.47</v>
+      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -491,14 +501,16 @@
           <t>KSP COMPUTERS</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>854.37</v>
-      </c>
+      <c r="C4" s="2" t="n">
+        <v>194.25</v>
+      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -506,17 +518,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 52218</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>206.81</v>
-      </c>
+          <t>KSP COMPUTERS</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>854.37</v>
+      </c>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -524,17 +538,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OFFICE DEPOT 3961</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>174.68</v>
-      </c>
+          <t>MISHKENOT REVIVIM 52218</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>206.81</v>
+      </c>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -542,17 +558,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OFFICE DEPOT 8886</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>252.99</v>
-      </c>
+          <t>OFFICE DEPOT 3961</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>174.68</v>
+      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -560,17 +578,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OFFICE DEPOT 9009</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>242.62</v>
-      </c>
+          <t>OFFICE DEPOT 8886</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>252.99</v>
+      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -578,17 +598,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>369.26</v>
-      </c>
+          <t>OFFICE DEPOT 9009</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>242.62</v>
+      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -596,17 +618,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>REFUND WOLT IL</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>94.17</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>369.26</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -614,17 +638,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SPOTIFY AB</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>23.9</v>
+          <t>REFUND WOLT IL</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>94.17</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -632,17 +658,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>STEAM PURCHASE</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>61.35</v>
-      </c>
+          <t>SPOTIFY AB</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -650,17 +678,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TENBIS LTD</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>80.88</v>
-      </c>
+          <t>STEAM PURCHASE</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -668,35 +698,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YANGO 269501</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>43.21</v>
-      </c>
+          <t>TENBIS LTD</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>80.88</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45537</v>
+        <v>45536</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AIRBNB * HMXQ74164</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>459.03</v>
-      </c>
+          <t>YANGO 269501</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -704,17 +738,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AIRBNB * HMXQ96184</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>177.66</v>
-      </c>
+          <t>AIRBNB * HMXQ74164</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>459.03</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -722,17 +758,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ALLTECH INSURANCE AGENCY</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>312</v>
-      </c>
+          <t>AIRBNB * HMXQ96184</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>177.66</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -740,17 +778,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>19.29</v>
-      </c>
+          <t>ALLTECH INSURANCE AGENCY</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -758,17 +798,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ARCAFFE DIZENGOFF</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>42.49</v>
-      </c>
+          <t>APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -776,17 +818,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BOOKING.COM 34646830</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>291.39</v>
-      </c>
+          <t>ARCAFFE DIZENGOFF</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -794,17 +838,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EL AL AIRLINES 859709</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1313.19</v>
-      </c>
+          <t>BOOKING.COM 34646830</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>291.39</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -812,17 +858,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KSP COMPUTERS</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>234.68</v>
-      </c>
+          <t>EL AL AIRLINES 859709</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1313.19</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -830,17 +878,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 44653</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>47.93</v>
-      </c>
+          <t>KSP COMPUTERS</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>234.68</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -848,17 +898,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OFFICE DEPOT 9461</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>47.92</v>
-      </c>
+          <t>MISHKENOT REVIVIM 44653</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>47.93</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -866,17 +918,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>168.53</v>
-      </c>
+          <t>OFFICE DEPOT 9461</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -884,17 +938,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PARTNER COMMUNICATION 415240</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>117.87</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>168.53</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -902,17 +958,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TENBIS LTD</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>119.74</v>
-      </c>
+          <t>PARTNER COMMUNICATION 415240</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>117.87</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -923,14 +981,16 @@
           <t>TLV PRINTHOUSE</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="2" t="n">
         <v>345.01</v>
       </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -941,14 +1001,16 @@
           <t>UBER *TRIP 308094</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="2" t="n">
         <v>91.58</v>
       </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -959,14 +1021,16 @@
           <t>WOLT IL 388872</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="2" t="n">
         <v>90.59</v>
       </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -977,14 +1041,16 @@
           <t>YANGO 682632</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="2" t="n">
         <v>62.97</v>
       </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -995,14 +1061,16 @@
           <t>BOOKING.COM 84271091</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="2" t="n">
         <v>183.77</v>
       </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
+      <c r="F32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1013,14 +1081,16 @@
           <t>CARD FEE ANNUAL</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="2" t="n">
         <v>12</v>
       </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1028,17 +1098,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GITHUB INC 8666982</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>21</v>
-      </c>
+          <t>FX COMMISSION 000010</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1046,17 +1118,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NOTION LABS INC</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>16</v>
-      </c>
+          <t>FX COMMISSION 000020</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1064,17 +1138,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OFFICE DEPOT 0169</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>77.27</v>
-      </c>
+          <t>FX COMMISSION 000030</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1082,17 +1158,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SHUFERSAL DEAL 6110</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>181.21</v>
-      </c>
+          <t>GITHUB INC 8666982</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1100,17 +1178,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>STEAM PURCHASE</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>114.02</v>
-      </c>
+          <t>NOTION LABS INC</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1118,17 +1198,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TAX AUTHORITY VAT PAYMENT</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>4752.27</v>
-      </c>
+          <t>OFFICE DEPOT 0169</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>77.27</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1136,71 +1218,79 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WIRE FEE INTERNATIONAL</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>25</v>
-      </c>
+          <t>SHUFERSAL DEAL 6110</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>181.21</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45539</v>
+        <v>45538</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AIRBNB * HMXQ11839</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>580.3200000000001</v>
-      </c>
+          <t>STEAM PURCHASE</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>114.02</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45539</v>
+        <v>45538</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ALLTECH INSURANCE AGENCY</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>312</v>
-      </c>
+          <t>TAX AUTHORITY VAT PAYMENT</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>4752.27</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45539</v>
+        <v>45538</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BOOKING.COM 53673591</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>267.19</v>
-      </c>
+          <t>WIRE FEE INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -1208,17 +1298,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LEUMIT SERVICES LTD</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>150</v>
-      </c>
+          <t>AIRBNB * HMXQ11839</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>580.3200000000001</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -1226,17 +1318,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 37553</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>54.61</v>
-      </c>
+          <t>ALLTECH INSURANCE AGENCY</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -1244,17 +1338,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PAYPAL *ENVATO</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>30.28</v>
-      </c>
+          <t>BOOKING.COM 53673591</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>267.19</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1262,17 +1358,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PAYPAL *UDEMY</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>24.1</v>
-      </c>
+          <t>LEUMIT SERVICES LTD</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -1280,17 +1378,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SUPER-PHARM 2405</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>167.12</v>
-      </c>
+          <t>MISHKENOT REVIVIM 37553</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -1298,17 +1398,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TENBIS LTD</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>99.73</v>
-      </c>
+          <t>PAYPAL *ENVATO</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>30.28</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -1316,71 +1418,79 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TENBIS LTD</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>111.3</v>
-      </c>
+          <t>PAYPAL *UDEMY</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45540</v>
+        <v>45539</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ALLTECH INSURANCE AGENCY</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>312</v>
-      </c>
+          <t>SUPER-PHARM 2405</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>167.12</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45540</v>
+        <v>45539</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CAFE NIMROD</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>43.68</v>
-      </c>
+          <t>TENBIS LTD</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>99.73</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45540</v>
+        <v>45539</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CAFE NIMROD</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>34.44</v>
-      </c>
+          <t>TENBIS LTD</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -1388,17 +1498,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EL AL AIRLINES 115600</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1455.36</v>
-      </c>
+          <t>ALLTECH INSURANCE AGENCY</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -1406,17 +1518,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FIGMA INC</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>15</v>
-      </c>
+          <t>CAFE NIMROD</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -1424,17 +1538,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LEUMIT SERVICES LTD</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>150</v>
-      </c>
+          <t>CAFE NIMROD</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>34.44</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -1442,17 +1558,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NETFLIX.COM</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>54.9</v>
-      </c>
+          <t>EL AL AIRLINES 115600</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1455.36</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -1460,17 +1578,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>450.79</v>
-      </c>
+          <t>FIGMA INC</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -1478,17 +1598,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>453.52</v>
-      </c>
+          <t>LEUMIT SERVICES LTD</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -1496,17 +1618,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PAYPAL *ENVATO</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>55.83</v>
-      </c>
+          <t>NETFLIX.COM</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -1514,17 +1638,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PAYPAL *UDEMY</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>48.15</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>450.79</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -1532,17 +1658,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RAMI LEVY</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>111.17</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>453.52</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -1550,17 +1678,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RAMI LEVY</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>320.89</v>
-      </c>
+          <t>PAYPAL *ENVATO</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -1568,17 +1698,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SUPER-PHARM 3033</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>70.84</v>
-      </c>
+          <t>PAYPAL *UDEMY</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -1586,17 +1718,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>116.11</v>
-      </c>
+          <t>RAMI LEVY</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>111.17</v>
+      </c>
+      <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -1604,71 +1738,79 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YANGO 070233</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>66</v>
-      </c>
+          <t>RAMI LEVY</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>320.89</v>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45541</v>
+        <v>45540</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ARCAFFE DIZENGOFF</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>23.18</v>
-      </c>
+          <t>SUPER-PHARM 3033</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>70.84</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45541</v>
+        <v>45540</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CELLCOM ISRAEL</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>59.9</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>116.11</v>
+      </c>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>45541</v>
+        <v>45540</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FX COMMISSION 083748</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>21.28</v>
-      </c>
+          <t>YANGO 070233</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -1676,17 +1818,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FX COMMISSION 427108</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>9.24</v>
-      </c>
+          <t>ARCAFFE DIZENGOFF</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -1694,17 +1838,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LEUMIT SERVICES LTD</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>150</v>
-      </c>
+          <t>CELLCOM ISRAEL</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -1712,17 +1858,19 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>294.24</v>
-      </c>
+          <t>FX COMMISSION 083748</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -1730,71 +1878,79 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>231.71</v>
-      </c>
+          <t>FX COMMISSION 427108</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>45542</v>
+        <v>45541</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ALLTECH INSURANCE AGENCY</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>312</v>
-      </c>
+          <t>LEUMIT SERVICES LTD</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>45542</v>
+        <v>45541</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ALLTECH INSURANCE AGENCY</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>312</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>294.24</v>
+      </c>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>45542</v>
+        <v>45541</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ALLTECH INSURANCE AGENCY</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>312</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>231.71</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -1802,17 +1958,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BEZEQ INTERNATIONAL</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>99</v>
-      </c>
+          <t>ALLTECH INSURANCE AGENCY</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -1820,17 +1978,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GETT TAXI 068155</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>69.81</v>
-      </c>
+          <t>ALLTECH INSURANCE AGENCY</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -1838,17 +1998,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KSP COMPUTERS</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>489.57</v>
-      </c>
+          <t>ALLTECH INSURANCE AGENCY</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -1856,17 +2018,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LEUMIT SERVICES LTD</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>150</v>
-      </c>
+          <t>BEZEQ INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -1874,17 +2038,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PAYPAL *ENVATO</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>45.78</v>
-      </c>
+          <t>GETT TAXI 068155</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -1892,17 +2058,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TLV PRINTHOUSE</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>249.28</v>
-      </c>
+          <t>KSP COMPUTERS</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>489.57</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -1910,17 +2078,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TLV PRINTHOUSE</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>92.77</v>
-      </c>
+          <t>LEUMIT SERVICES LTD</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -1931,14 +2101,16 @@
           <t>TLV PRINTHOUSE</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>305.61</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>249.28</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -1946,17 +2118,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WEWORK TLV</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1350</v>
-      </c>
+          <t>TLV PRINTHOUSE</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -1964,35 +2138,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ZOOM.US 495552</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>14.99</v>
-      </c>
+          <t>WEWORK TLV</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>45543</v>
+        <v>45542</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AWS EMEA 51106311</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>176.85</v>
-      </c>
+          <t>ZOOM.US 495552</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
+      <c r="F87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -2000,17 +2178,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BOOKING.COM 57446810</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>134.49</v>
-      </c>
+          <t>AWS EMEA 51106311</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>176.85</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -2018,17 +2198,19 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CERCLI LTD 558117</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>450</v>
-      </c>
+          <t>BOOKING.COM 57446810</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>134.49</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -2036,17 +2218,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EL AL AIRLINES 703382</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>1340.57</v>
-      </c>
+          <t>CERCLI LTD 558117</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -2054,17 +2238,19 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GETT TAXI 578044</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>94.36</v>
-      </c>
+          <t>EL AL AIRLINES 703382</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>1340.57</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -2072,17 +2258,19 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>INCOMING TRANSFER NORTHWIND STUDIO INV-8197</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>4319.74</v>
-      </c>
+          <t>GETT TAXI 578044</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>94.36</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -2090,17 +2278,19 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JETBRAINS S.R.O.</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>24.9</v>
+          <t>INCOMING TRANSFER NORTHWIND STUDIO INV-8197</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>4319.74</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -2108,17 +2298,19 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PAYPAL *ENVATO</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>53.51</v>
-      </c>
+          <t>JETBRAINS S.R.O.</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -2126,17 +2318,19 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>RAMI LEVY</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>179.51</v>
-      </c>
+          <t>PAYPAL *ENVATO</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -2144,17 +2338,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SLACK TECHNOLOGIES 424321</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>32.5</v>
-      </c>
+          <t>RAMI LEVY</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>179.51</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -2162,17 +2358,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SUPER-PHARM 2237</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>165.79</v>
-      </c>
+          <t>SLACK TECHNOLOGIES 424321</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -2180,17 +2378,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>99.98999999999999</v>
-      </c>
+          <t>SUPER-PHARM 2237</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>165.79</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -2198,35 +2398,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>UBER *TRIP 529067</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>33.51</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>45544</v>
+        <v>45543</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DOCUSIGN 87233630</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>25</v>
-      </c>
+          <t>UBER *TRIP 529067</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>33.51</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -2234,17 +2438,19 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GOOGLE*GSUITE 798448</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>46.8</v>
-      </c>
+          <t>DOCUSIGN 87233630</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
+      <c r="F101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -2252,17 +2458,19 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LEUMIT SERVICES LTD</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>150</v>
-      </c>
+          <t>GOOGLE*GSUITE 798448</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -2270,17 +2478,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PAYONEER WITHDRAWAL 01587388</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>6943.43</v>
-      </c>
+          <t>LEUMIT SERVICES LTD</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -2288,17 +2498,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SUPER-PHARM 8407</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>102.95</v>
+          <t>PAYONEER WITHDRAWAL 01587388</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>6943.43</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -2306,17 +2518,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>UBER *TRIP 395040</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>71.52</v>
-      </c>
+          <t>SUPER-PHARM 8407</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -2324,35 +2538,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>WOLT IL 211263</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>68.77</v>
-      </c>
+          <t>UBER *TRIP 395040</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>71.52</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>45545</v>
+        <v>45544</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ALLTECH INSURANCE AGENCY</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>312</v>
-      </c>
+          <t>WOLT IL 211263</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>68.77</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -2360,17 +2578,19 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ARCAFFE DIZENGOFF</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>42.91</v>
-      </c>
+          <t>ALLTECH INSURANCE AGENCY</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -2378,17 +2598,19 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BOOKING.COM 59522548</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>133.67</v>
-      </c>
+          <t>ARCAFFE DIZENGOFF</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -2396,17 +2618,19 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CAFE NIMROD</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>31.45</v>
-      </c>
+          <t>BOOKING.COM 59522548</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>133.67</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -2417,14 +2641,16 @@
           <t>CAFE NIMROD</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>31.49</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -2435,14 +2661,16 @@
           <t>CAFE NIMROD</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v>22.27</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>31.49</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -2450,17 +2678,19 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HETZNER ONLINE GMBH</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>39.69</v>
-      </c>
+          <t>CAFE NIMROD</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -2468,17 +2698,19 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>INCOMING TRANSFER ACME DIGITAL LTD INV-3558</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>6811.63</v>
-      </c>
+          <t>HETZNER ONLINE GMBH</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -2486,17 +2718,19 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 12777</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>60.38</v>
+          <t>INCOMING TRANSFER ACME DIGITAL LTD INV-3558</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>6811.63</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -2504,17 +2738,19 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 36804</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>82.69</v>
-      </c>
+          <t>MISHKENOT REVIVIM 12777</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>60.38</v>
+      </c>
+      <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -2522,17 +2758,19 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 77344</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>93.06</v>
-      </c>
+          <t>MISHKENOT REVIVIM 36804</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -2540,17 +2778,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 79191</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>208.87</v>
-      </c>
+          <t>MISHKENOT REVIVIM 77344</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>93.06</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -2558,17 +2798,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>OFFICE DEPOT 1205</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>99.76000000000001</v>
-      </c>
+          <t>MISHKENOT REVIVIM 79191</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>208.87</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -2576,17 +2818,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PAYPAL *UDEMY</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>16.99</v>
-      </c>
+          <t>OFFICE DEPOT 1205</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -2594,17 +2838,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RAMI LEVY</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>199.72</v>
-      </c>
+          <t>PAYPAL *UDEMY</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -2615,14 +2861,16 @@
           <t>RAMI LEVY</t>
         </is>
       </c>
-      <c r="C122" t="n">
-        <v>311.84</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>199.72</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -2630,35 +2878,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SHUFERSAL DEAL 2845</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>156.3</v>
-      </c>
+          <t>RAMI LEVY</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>311.84</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ALLTECH INSURANCE AGENCY</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>312</v>
-      </c>
+          <t>SHUFERSAL DEAL 2845</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>156.3</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -2669,14 +2921,16 @@
           <t>ALLTECH INSURANCE AGENCY</t>
         </is>
       </c>
-      <c r="C125" t="n">
+      <c r="C125" s="2" t="n">
         <v>312</v>
       </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -2684,17 +2938,19 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ARCAFFE DIZENGOFF</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>53.03</v>
-      </c>
+          <t>ALLTECH INSURANCE AGENCY</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -2702,17 +2958,19 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EL AL AIRLINES 233703</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>1995.13</v>
-      </c>
+          <t>ARCAFFE DIZENGOFF</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -2720,17 +2978,19 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 74078</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>102.16</v>
-      </c>
+          <t>EL AL AIRLINES 233703</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>1995.13</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -2738,17 +2998,19 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PAYPAL *ENVATO</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>24.68</v>
-      </c>
+          <t>MISHKENOT REVIVIM 74078</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>102.16</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -2756,17 +3018,19 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SUPER-PHARM 2294</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>55.17</v>
-      </c>
+          <t>PAYPAL *ENVATO</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -2774,35 +3038,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>WOLT IL 842639</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>108.68</v>
-      </c>
+          <t>SUPER-PHARM 2294</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>45547</v>
+        <v>45546</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ALLTECH INSURANCE AGENCY</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>312</v>
-      </c>
+          <t>WOLT IL 842639</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>108.68</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -2810,17 +3078,19 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 97855</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>196.35</v>
-      </c>
+          <t>ALLTECH INSURANCE AGENCY</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -2828,35 +3098,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>167.06</v>
-      </c>
+          <t>MISHKENOT REVIVIM 97855</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>196.35</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>45548</v>
+        <v>45547</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>25.75</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>167.06</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -2867,14 +3141,16 @@
           <t>APPLE.COM/BILL</t>
         </is>
       </c>
-      <c r="C136" t="n">
-        <v>34.3</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -2882,17 +3158,19 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ARCAFFE DIZENGOFF</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>46.03</v>
-      </c>
+          <t>APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -2900,17 +3178,19 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>INCOMING TRANSFER NORTHWIND STUDIO INV-3289</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>4146.56</v>
-      </c>
+          <t>ARCAFFE DIZENGOFF</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -2918,17 +3198,19 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>503.95</v>
+          <t>INCOMING TRANSFER NORTHWIND STUDIO INV-3289</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n">
+        <v>4146.56</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -2936,17 +3218,19 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SUPER-PHARM 1113</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>53.59</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>503.95</v>
+      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -2954,17 +3238,19 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SUPER-PHARM 6588</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>52.89</v>
-      </c>
+          <t>SUPER-PHARM 1113</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>53.59</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -2972,17 +3258,19 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>158.13</v>
-      </c>
+          <t>SUPER-PHARM 6588</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -2990,17 +3278,19 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TENBIS LTD</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>84.66</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>158.13</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -3008,35 +3298,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TLV PRINTHOUSE</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>281.01</v>
-      </c>
+          <t>TENBIS LTD</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>84.66</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>45549</v>
+        <v>45548</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CARD FEE ANNUAL</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>12</v>
-      </c>
+          <t>TLV PRINTHOUSE</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>281.01</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -3044,17 +3338,19 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EL AL AIRLINES 713589</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>1579</v>
-      </c>
+          <t>CARD FEE ANNUAL</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -3062,17 +3358,19 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>OFFICE DEPOT 1811</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>230.63</v>
-      </c>
+          <t>EL AL AIRLINES 713589</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>1579</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -3080,17 +3378,19 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>170.06</v>
-      </c>
+          <t>OFFICE DEPOT 1811</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>230.63</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -3098,17 +3398,19 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TENBIS LTD</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>77.18000000000001</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>170.06</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -3116,35 +3418,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TLV PRINTHOUSE</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>158.23</v>
-      </c>
+          <t>TENBIS LTD</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>77.18000000000001</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>45550</v>
+        <v>45549</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ARCAFFE DIZENGOFF</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>22.73</v>
-      </c>
+          <t>TLV PRINTHOUSE</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>158.23</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -3152,35 +3458,25 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>522.97</v>
-      </c>
+          <t>ARCAFFE DIZENGOFF</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F152" s="2" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
-        <v>45550</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>RAMI LEVY</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>141.03</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
+      <c r="A153" s="1" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n"/>
+      <c r="F153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -3188,17 +3484,19 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SHUFERSAL DEAL 7412</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>79.97</v>
+          <t>INCOMING TRANSFER ACME DIGITAL LTD INV-9001</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>123456.78</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -3206,17 +3504,19 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>174.2</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>522.97</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -3224,17 +3524,19 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>148.38</v>
-      </c>
+          <t>RAMI LEVY</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>141.03</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -3242,71 +3544,79 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TENBIS LTD</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>127.53</v>
-      </c>
+          <t>SHUFERSAL DEAL 7412</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>45551</v>
+        <v>45550</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>26.81</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>174.2</v>
+      </c>
+      <c r="D158" s="2" t="n"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>45551</v>
+        <v>45550</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>36.92</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>148.38</v>
+      </c>
+      <c r="D159" s="2" t="n"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>45551</v>
+        <v>45550</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ARCAFFE DIZENGOFF</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>54.69</v>
-      </c>
+          <t>TENBIS LTD</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>127.53</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -3314,17 +3624,19 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CAFE NIMROD</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>25.55</v>
-      </c>
+          <t>APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="D161" s="2" t="n"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -3332,17 +3644,19 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CAFE NIMROD</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>20.89</v>
-      </c>
+          <t>APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -3350,17 +3664,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>RAMI LEVY</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>327.26</v>
-      </c>
+          <t>ARCAFFE DIZENGOFF</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -3368,17 +3684,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>205.6</v>
-      </c>
+          <t>CAFE NIMROD</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="D164" s="2" t="n"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -3386,17 +3704,19 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>146.69</v>
-      </c>
+          <t>CAFE NIMROD</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="D165" s="2" t="n"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -3404,17 +3724,19 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>UBER *TRIP 061580</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>71.34</v>
-      </c>
+          <t>RAMI LEVY</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>327.26</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -3422,17 +3744,19 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>WOLT IL 001013</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>105.72</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="D167" s="2" t="n"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -3440,71 +3764,79 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>YANGO 484953</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>67.91</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>146.69</v>
+      </c>
+      <c r="D168" s="2" t="n"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>45552</v>
+        <v>45551</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>AIRBNB * HMXQ34007</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>315.47</v>
-      </c>
+          <t>UBER *TRIP 061580</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>71.34</v>
+      </c>
+      <c r="D169" s="2" t="n"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>45552</v>
+        <v>45551</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
-        </is>
-      </c>
-      <c r="C170" t="n">
-        <v>39.55</v>
-      </c>
+          <t>WOLT IL 001013</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>105.72</v>
+      </c>
+      <c r="D170" s="2" t="n"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>45552</v>
+        <v>45551</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ARCAFFE DIZENGOFF</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
-        <v>53.3</v>
-      </c>
+          <t>YANGO 484953</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>67.91</v>
+      </c>
+      <c r="D171" s="2" t="n"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -3512,17 +3844,19 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>BOOKING.COM 83800788</t>
-        </is>
-      </c>
-      <c r="C172" t="n">
-        <v>225.88</v>
-      </c>
+          <t>AIRBNB * HMXQ34007</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n">
+        <v>315.47</v>
+      </c>
+      <c r="D172" s="2" t="n"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
+      <c r="F172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -3530,17 +3864,19 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CAFE NIMROD</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
-        <v>43.83</v>
-      </c>
+          <t>APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="D173" s="2" t="n"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -3548,17 +3884,19 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PAYPAL *UDEMY</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
-        <v>38.15</v>
-      </c>
+          <t>ARCAFFE DIZENGOFF</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D174" s="2" t="n"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -3566,17 +3904,19 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PAYPAL *UDEMY</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
-        <v>25.64</v>
-      </c>
+          <t>BOOKING.COM 83800788</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v>225.88</v>
+      </c>
+      <c r="D175" s="2" t="n"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -3584,17 +3924,19 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>RAMI LEVY</t>
-        </is>
-      </c>
-      <c r="C176" t="n">
-        <v>358.47</v>
-      </c>
+          <t>CAFE NIMROD</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="D176" s="2" t="n"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -3602,17 +3944,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SHUFERSAL DEAL 5486</t>
-        </is>
-      </c>
-      <c r="C177" t="n">
-        <v>331.85</v>
-      </c>
+          <t>PAYPAL *UDEMY</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="D177" s="2" t="n"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -3620,71 +3964,79 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>WOLT IL 124315</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>78.5</v>
-      </c>
+          <t>PAYPAL *UDEMY</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="D178" s="2" t="n"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>45553</v>
+        <v>45552</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>BOOKING.COM 36189720</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>218.97</v>
-      </c>
+          <t>RAMI LEVY</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>358.47</v>
+      </c>
+      <c r="D179" s="2" t="n"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>45553</v>
+        <v>45552</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>BOOKING.COM 40717579</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>275.31</v>
-      </c>
+          <t>SHUFERSAL DEAL 5486</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="n">
+        <v>331.85</v>
+      </c>
+      <c r="D180" s="2" t="n"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>45553</v>
+        <v>45552</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GETT TAXI 997055</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
-        <v>38.47</v>
-      </c>
+          <t>WOLT IL 124315</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="D181" s="2" t="n"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -3692,17 +4044,19 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>LEUMIT SERVICES LTD</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
-        <v>150</v>
-      </c>
+          <t>BOOKING.COM 36189720</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n">
+        <v>218.97</v>
+      </c>
+      <c r="D182" s="2" t="n"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -3710,17 +4064,19 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C183" t="n">
-        <v>162.9</v>
-      </c>
+          <t>BOOKING.COM 40717579</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>275.31</v>
+      </c>
+      <c r="D183" s="2" t="n"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -3728,17 +4084,19 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C184" t="n">
-        <v>349.57</v>
-      </c>
+          <t>GETT TAXI 997055</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="n">
+        <v>38.47</v>
+      </c>
+      <c r="D184" s="2" t="n"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -3746,17 +4104,19 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PAYPAL *UDEMY</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>61.64</v>
-      </c>
+          <t>LEUMIT SERVICES LTD</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D185" s="2" t="n"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -3764,17 +4124,19 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>STEAM PURCHASE</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>60.75</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="D186" s="2" t="n"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -3782,17 +4144,19 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SUPER-PHARM 2492</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>31.64</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="D187" s="2" t="n"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -3800,71 +4164,79 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>YANGO 535102</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>38.37</v>
-      </c>
+          <t>PAYPAL *UDEMY</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="n">
+        <v>61.64</v>
+      </c>
+      <c r="D188" s="2" t="n"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>45554</v>
+        <v>45553</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>AIRBNB * HMXQ86148</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>348.67</v>
-      </c>
+          <t>STEAM PURCHASE</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="D189" s="2" t="n"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>45554</v>
+        <v>45553</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ARCAFFE DIZENGOFF</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>50.35</v>
-      </c>
+          <t>SUPER-PHARM 2492</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="D190" s="2" t="n"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>45554</v>
+        <v>45553</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ARCAFFE DIZENGOFF</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>28.23</v>
-      </c>
+          <t>YANGO 535102</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="D191" s="2" t="n"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -3872,17 +4244,19 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>INCOMING TRANSFER ACME DIGITAL LTD INV-7309</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>15001.63</v>
-      </c>
+          <t>AIRBNB * HMXQ86148</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="n">
+        <v>348.67</v>
+      </c>
+      <c r="D192" s="2" t="n"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -3890,17 +4264,19 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>338.7</v>
-      </c>
+          <t>ARCAFFE DIZENGOFF</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="D193" s="2" t="n"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -3908,17 +4284,19 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PAYONEER WITHDRAWAL 10517773</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>6647.19</v>
-      </c>
+          <t>ARCAFFE DIZENGOFF</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="D194" s="2" t="n"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -3926,17 +4304,19 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PAYONEER WITHDRAWAL 80087122</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>2136.7</v>
+          <t>INCOMING TRANSFER ACME DIGITAL LTD INV-7309</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="n"/>
+      <c r="D195" s="2" t="n">
+        <v>15001.63</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -3944,17 +4324,19 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SHUFERSAL DEAL 0792</t>
-        </is>
-      </c>
-      <c r="C196" t="n">
-        <v>153.07</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="D196" s="2" t="n"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -3962,17 +4344,19 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TLV PRINTHOUSE</t>
-        </is>
-      </c>
-      <c r="C197" t="n">
-        <v>394.28</v>
+          <t>PAYONEER WITHDRAWAL 10517773</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n"/>
+      <c r="D197" s="2" t="n">
+        <v>6647.19</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -3980,71 +4364,79 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>WOLT IL 436046</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
-        <v>55.68</v>
+          <t>PAYONEER WITHDRAWAL 80087122</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="n"/>
+      <c r="D198" s="2" t="n">
+        <v>2136.7</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>45555</v>
+        <v>45554</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ALLTECH INSURANCE AGENCY</t>
-        </is>
-      </c>
-      <c r="C199" t="n">
-        <v>312</v>
-      </c>
+          <t>SHUFERSAL DEAL 0792</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="n">
+        <v>153.07</v>
+      </c>
+      <c r="D199" s="2" t="n"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>45555</v>
+        <v>45554</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>GETT TAXI 101256</t>
-        </is>
-      </c>
-      <c r="C200" t="n">
-        <v>107.86</v>
-      </c>
+          <t>TLV PRINTHOUSE</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="n">
+        <v>394.28</v>
+      </c>
+      <c r="D200" s="2" t="n"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>45555</v>
+        <v>45554</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>GETT TAXI 274455</t>
-        </is>
-      </c>
-      <c r="C201" t="n">
-        <v>53.97</v>
-      </c>
+          <t>WOLT IL 436046</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="D201" s="2" t="n"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -4052,17 +4444,19 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>KSP COMPUTERS</t>
-        </is>
-      </c>
-      <c r="C202" t="n">
-        <v>253</v>
-      </c>
+          <t>ALLTECH INSURANCE AGENCY</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="D202" s="2" t="n"/>
       <c r="E202" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -4070,17 +4464,19 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 31547</t>
-        </is>
-      </c>
-      <c r="C203" t="n">
-        <v>201.35</v>
-      </c>
+          <t>GETT TAXI 101256</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>107.86</v>
+      </c>
+      <c r="D203" s="2" t="n"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -4088,17 +4484,21 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>OFFICE DEPOT 1537</t>
-        </is>
-      </c>
-      <c r="C204" t="n">
-        <v>248.5</v>
-      </c>
+          <t>COFFEE SHOP ABC</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>12.3O</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="n"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -4106,17 +4506,19 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PAYPAL *ENVATO</t>
-        </is>
-      </c>
-      <c r="C205" t="n">
-        <v>33.3</v>
-      </c>
+          <t>GETT TAXI 274455</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="D205" s="2" t="n"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -4124,89 +4526,99 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SHUFERSAL DEAL 5407</t>
-        </is>
-      </c>
-      <c r="C206" t="n">
-        <v>147.44</v>
-      </c>
+          <t>KSP COMPUTERS</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="D206" s="2" t="n"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>45556</v>
+        <v>45555</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>BOOKING.COM 86552704</t>
-        </is>
-      </c>
-      <c r="C207" t="n">
-        <v>305.34</v>
-      </c>
+          <t>MISHKENOT REVIVIM 31547</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="n">
+        <v>201.35</v>
+      </c>
+      <c r="D207" s="2" t="n"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>45556</v>
+        <v>45555</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>EL AL AIRLINES 844467</t>
-        </is>
-      </c>
-      <c r="C208" t="n">
-        <v>2200.93</v>
-      </c>
+          <t>OFFICE DEPOT 1537</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="D208" s="2" t="n"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>45556</v>
+        <v>45555</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>GETT TAXI 265887</t>
-        </is>
-      </c>
-      <c r="C209" t="n">
-        <v>59.46</v>
-      </c>
+          <t>PAYPAL *ENVATO</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D209" s="2" t="n"/>
       <c r="E209" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>45556</v>
+        <v>45555</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>INCOMING SEPA CONTOSO GMBH INV-2364</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>1568.26</v>
-      </c>
+          <t>SHUFERSAL DEAL 5407</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="n">
+        <v>147.44</v>
+      </c>
+      <c r="D210" s="2" t="n"/>
       <c r="E210" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
@@ -4214,17 +4626,19 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PAYPAL *UDEMY</t>
-        </is>
-      </c>
-      <c r="C211" t="n">
-        <v>64.06999999999999</v>
-      </c>
+          <t>BOOKING.COM 86552704</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="n">
+        <v>305.34</v>
+      </c>
+      <c r="D211" s="2" t="n"/>
       <c r="E211" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -4232,17 +4646,19 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SHUFERSAL DEAL 0571</t>
-        </is>
-      </c>
-      <c r="C212" t="n">
-        <v>360.48</v>
-      </c>
+          <t>EL AL AIRLINES 844467</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="n">
+        <v>2200.93</v>
+      </c>
+      <c r="D212" s="2" t="n"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -4250,17 +4666,19 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>STEAM PURCHASE</t>
-        </is>
-      </c>
-      <c r="C213" t="n">
-        <v>128.29</v>
-      </c>
+          <t>GETT TAXI 265887</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="D213" s="2" t="n"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -4268,17 +4686,19 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>TENBIS LTD</t>
-        </is>
-      </c>
-      <c r="C214" t="n">
-        <v>80.42</v>
+          <t>INCOMING SEPA CONTOSO GMBH INV-2364</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="n"/>
+      <c r="D214" s="2" t="n">
+        <v>1568.26</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -4286,17 +4706,19 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>TLV PRINTHOUSE</t>
-        </is>
-      </c>
-      <c r="C215" t="n">
-        <v>369.86</v>
-      </c>
+          <t>PAYPAL *UDEMY</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="D215" s="2" t="n"/>
       <c r="E215" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -4304,17 +4726,19 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>TLV PRINTHOUSE</t>
-        </is>
-      </c>
-      <c r="C216" t="n">
-        <v>402.9</v>
-      </c>
+          <t>SHUFERSAL DEAL 0571</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="n">
+        <v>360.48</v>
+      </c>
+      <c r="D216" s="2" t="n"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -4322,17 +4746,19 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>UBER *TRIP 026091</t>
-        </is>
-      </c>
-      <c r="C217" t="n">
-        <v>40.42</v>
-      </c>
+          <t>STEAM PURCHASE</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="n">
+        <v>128.29</v>
+      </c>
+      <c r="D217" s="2" t="n"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -4340,17 +4766,19 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>UBER *TRIP 590710</t>
-        </is>
-      </c>
-      <c r="C218" t="n">
-        <v>62.58</v>
-      </c>
+          <t>TENBIS LTD</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="n">
+        <v>80.42</v>
+      </c>
+      <c r="D218" s="2" t="n"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -4358,89 +4786,99 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>YANGO 142787</t>
-        </is>
-      </c>
-      <c r="C219" t="n">
-        <v>48.45</v>
-      </c>
+          <t>TLV PRINTHOUSE</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="D219" s="2" t="n"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>45557</v>
+        <v>45556</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
-        </is>
-      </c>
-      <c r="C220" t="n">
-        <v>17.62</v>
-      </c>
+          <t>TLV PRINTHOUSE</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="n">
+        <v>402.9</v>
+      </c>
+      <c r="D220" s="2" t="n"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>45557</v>
+        <v>45556</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
-        </is>
-      </c>
-      <c r="C221" t="n">
-        <v>38.14</v>
-      </c>
+          <t>UBER *TRIP 026091</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="D221" s="2" t="n"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>45557</v>
+        <v>45556</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
-        </is>
-      </c>
-      <c r="C222" t="n">
-        <v>18.93</v>
-      </c>
+          <t>UBER *TRIP 590710</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="D222" s="2" t="n"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>45557</v>
+        <v>45556</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ARCAFFE DIZENGOFF</t>
-        </is>
-      </c>
-      <c r="C223" t="n">
-        <v>36.12</v>
-      </c>
+          <t>YANGO 142787</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="D223" s="2" t="n"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -4448,17 +4886,19 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>EL AL AIRLINES 762992</t>
-        </is>
-      </c>
-      <c r="C224" t="n">
-        <v>2358.27</v>
-      </c>
+          <t>APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="D224" s="2" t="n"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -4466,17 +4906,19 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>KSP COMPUTERS</t>
-        </is>
-      </c>
-      <c r="C225" t="n">
-        <v>747.92</v>
-      </c>
+          <t>APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="D225" s="2" t="n"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -4484,89 +4926,99 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C226" t="n">
-        <v>363.4</v>
-      </c>
+          <t>APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="D226" s="2" t="n"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>45558</v>
+        <v>45557</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>AIRBNB * HMXQ55105</t>
-        </is>
-      </c>
-      <c r="C227" t="n">
-        <v>317.85</v>
-      </c>
+          <t>ARCAFFE DIZENGOFF</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="D227" s="2" t="n"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>45558</v>
+        <v>45557</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>EL AL AIRLINES 720262</t>
-        </is>
-      </c>
-      <c r="C228" t="n">
-        <v>1922.39</v>
-      </c>
+          <t>EL AL AIRLINES 762992</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="n">
+        <v>2358.27</v>
+      </c>
+      <c r="D228" s="2" t="n"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>45558</v>
+        <v>45557</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>KSP COMPUTERS</t>
         </is>
       </c>
-      <c r="C229" t="n">
-        <v>329.34</v>
-      </c>
+      <c r="C229" s="2" t="n">
+        <v>747.92</v>
+      </c>
+      <c r="D229" s="2" t="n"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>45558</v>
+        <v>45557</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>KSP COMPUTERS</t>
-        </is>
-      </c>
-      <c r="C230" t="n">
-        <v>565.49</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="D230" s="2" t="n"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -4574,17 +5026,19 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>KSP COMPUTERS</t>
-        </is>
-      </c>
-      <c r="C231" t="n">
-        <v>615.47</v>
-      </c>
+          <t>AIRBNB * HMXQ55105</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="n">
+        <v>317.85</v>
+      </c>
+      <c r="D231" s="2" t="n"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -4592,17 +5046,19 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>LEUMIT SERVICES LTD</t>
-        </is>
-      </c>
-      <c r="C232" t="n">
-        <v>150</v>
-      </c>
+          <t>EL AL AIRLINES 720262</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="n">
+        <v>1922.39</v>
+      </c>
+      <c r="D232" s="2" t="n"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -4610,17 +5066,19 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 28994</t>
-        </is>
-      </c>
-      <c r="C233" t="n">
-        <v>157.71</v>
-      </c>
+          <t>KSP COMPUTERS</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="n">
+        <v>329.34</v>
+      </c>
+      <c r="D233" s="2" t="n"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -4628,17 +5086,19 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C234" t="n">
-        <v>311.06</v>
-      </c>
+          <t>KSP COMPUTERS</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="n">
+        <v>565.49</v>
+      </c>
+      <c r="D234" s="2" t="n"/>
       <c r="E234" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -4646,17 +5106,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SHUFERSAL DEAL 2314</t>
-        </is>
-      </c>
-      <c r="C235" t="n">
-        <v>291.58</v>
-      </c>
+          <t>KSP COMPUTERS</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="n">
+        <v>615.47</v>
+      </c>
+      <c r="D235" s="2" t="n"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -4664,89 +5126,99 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C236" t="n">
-        <v>119.52</v>
-      </c>
+          <t>LEUMIT SERVICES LTD</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D236" s="2" t="n"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>45559</v>
+        <v>45558</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>AIRBNB * HMXQ91232</t>
-        </is>
-      </c>
-      <c r="C237" t="n">
-        <v>314.91</v>
-      </c>
+          <t>MISHKENOT REVIVIM 28994</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="n">
+        <v>157.71</v>
+      </c>
+      <c r="D237" s="2" t="n"/>
       <c r="E237" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>45559</v>
+        <v>45558</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ALLTECH INSURANCE AGENCY</t>
-        </is>
-      </c>
-      <c r="C238" t="n">
-        <v>312</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="n">
+        <v>311.06</v>
+      </c>
+      <c r="D238" s="2" t="n"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>45559</v>
+        <v>45558</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
-        </is>
-      </c>
-      <c r="C239" t="n">
-        <v>39.06</v>
-      </c>
+          <t>SHUFERSAL DEAL 2314</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="n">
+        <v>291.58</v>
+      </c>
+      <c r="D239" s="2" t="n"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>45559</v>
+        <v>45558</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>BOOKING.COM 02071084</t>
-        </is>
-      </c>
-      <c r="C240" t="n">
-        <v>130.15</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="n">
+        <v>119.52</v>
+      </c>
+      <c r="D240" s="2" t="n"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -4754,17 +5226,19 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>CAFE NIMROD</t>
-        </is>
-      </c>
-      <c r="C241" t="n">
-        <v>43.59</v>
-      </c>
+          <t>AIRBNB * HMXQ91232</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="n">
+        <v>314.91</v>
+      </c>
+      <c r="D241" s="2" t="n"/>
       <c r="E241" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -4772,17 +5246,19 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 69401</t>
-        </is>
-      </c>
-      <c r="C242" t="n">
-        <v>65.37</v>
-      </c>
+          <t>ALLTECH INSURANCE AGENCY</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="D242" s="2" t="n"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -4790,17 +5266,19 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PAYPAL *ENVATO</t>
-        </is>
-      </c>
-      <c r="C243" t="n">
-        <v>26.8</v>
-      </c>
+          <t>APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="n">
+        <v>39.06</v>
+      </c>
+      <c r="D243" s="2" t="n"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -4808,17 +5286,19 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>SHUFERSAL DEAL 1943</t>
-        </is>
-      </c>
-      <c r="C244" t="n">
-        <v>147.95</v>
-      </c>
+          <t>BOOKING.COM 02071084</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="n">
+        <v>130.15</v>
+      </c>
+      <c r="D244" s="2" t="n"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -4826,17 +5306,19 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>SUPER-PHARM 0683</t>
-        </is>
-      </c>
-      <c r="C245" t="n">
-        <v>163.21</v>
-      </c>
+          <t>CAFE NIMROD</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="D245" s="2" t="n"/>
       <c r="E245" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -4844,89 +5326,99 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>WOLT IL 459129</t>
-        </is>
-      </c>
-      <c r="C246" t="n">
-        <v>156.03</v>
-      </c>
+          <t>MISHKENOT REVIVIM 69401</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="n">
+        <v>65.37</v>
+      </c>
+      <c r="D246" s="2" t="n"/>
       <c r="E246" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>45560</v>
+        <v>45559</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>GETT TAXI 623401</t>
-        </is>
-      </c>
-      <c r="C247" t="n">
-        <v>32.58</v>
-      </c>
+          <t>PAYPAL *ENVATO</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D247" s="2" t="n"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>45560</v>
+        <v>45559</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>OFFICE DEPOT 2212</t>
-        </is>
-      </c>
-      <c r="C248" t="n">
-        <v>119.44</v>
-      </c>
+          <t>SHUFERSAL DEAL 1943</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="n">
+        <v>147.95</v>
+      </c>
+      <c r="D248" s="2" t="n"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>45560</v>
+        <v>45559</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C249" t="n">
-        <v>280.07</v>
-      </c>
+          <t>SUPER-PHARM 0683</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="n">
+        <v>163.21</v>
+      </c>
+      <c r="D249" s="2" t="n"/>
       <c r="E249" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>45560</v>
+        <v>45559</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PAYPAL *ENVATO</t>
-        </is>
-      </c>
-      <c r="C250" t="n">
-        <v>42.61</v>
-      </c>
+          <t>WOLT IL 459129</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="n">
+        <v>156.03</v>
+      </c>
+      <c r="D250" s="2" t="n"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -4934,17 +5426,19 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>UBER *TRIP 232176</t>
-        </is>
-      </c>
-      <c r="C251" t="n">
-        <v>45.16</v>
-      </c>
+          <t>GETT TAXI 623401</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="D251" s="2" t="n"/>
       <c r="E251" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -4952,17 +5446,19 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>UBER *TRIP 445119</t>
-        </is>
-      </c>
-      <c r="C252" t="n">
-        <v>73.81</v>
-      </c>
+          <t>OFFICE DEPOT 2212</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="n">
+        <v>119.44</v>
+      </c>
+      <c r="D252" s="2" t="n"/>
       <c r="E252" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -4970,17 +5466,19 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>UBER *TRIP 943288</t>
-        </is>
-      </c>
-      <c r="C253" t="n">
-        <v>43.46</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="n">
+        <v>280.07</v>
+      </c>
+      <c r="D253" s="2" t="n"/>
       <c r="E253" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -4988,17 +5486,19 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>WOLT IL 466836</t>
-        </is>
-      </c>
-      <c r="C254" t="n">
-        <v>142.23</v>
-      </c>
+          <t>PAYPAL *ENVATO</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="D254" s="2" t="n"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -5006,89 +5506,99 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>WOLT IL 876854</t>
-        </is>
-      </c>
-      <c r="C255" t="n">
-        <v>48.05</v>
-      </c>
+          <t>UBER *TRIP 232176</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="D255" s="2" t="n"/>
       <c r="E255" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>45561</v>
+        <v>45560</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>OFFICE DEPOT 8640</t>
-        </is>
-      </c>
-      <c r="C256" t="n">
-        <v>46.02</v>
-      </c>
+          <t>UBER *TRIP 445119</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="n">
+        <v>73.81</v>
+      </c>
+      <c r="D256" s="2" t="n"/>
       <c r="E256" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>45561</v>
+        <v>45560</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C257" t="n">
-        <v>344.4</v>
-      </c>
+          <t>UBER *TRIP 943288</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="n">
+        <v>43.46</v>
+      </c>
+      <c r="D257" s="2" t="n"/>
       <c r="E257" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>45561</v>
+        <v>45560</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>STEAM PURCHASE</t>
-        </is>
-      </c>
-      <c r="C258" t="n">
-        <v>98.27</v>
-      </c>
+          <t>WOLT IL 466836</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="n">
+        <v>142.23</v>
+      </c>
+      <c r="D258" s="2" t="n"/>
       <c r="E258" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>45561</v>
+        <v>45560</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SUPER-PHARM 9992</t>
-        </is>
-      </c>
-      <c r="C259" t="n">
-        <v>60.7</v>
-      </c>
+          <t>WOLT IL 876854</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="D259" s="2" t="n"/>
       <c r="E259" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -5096,17 +5606,19 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C260" t="n">
-        <v>152.79</v>
-      </c>
+          <t>OFFICE DEPOT 8640</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="D260" s="2" t="n"/>
       <c r="E260" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -5114,17 +5626,19 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>UBER *TRIP 192402</t>
-        </is>
-      </c>
-      <c r="C261" t="n">
-        <v>43.76</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="n">
+        <v>344.4</v>
+      </c>
+      <c r="D261" s="2" t="n"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -5132,17 +5646,19 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>UBER *TRIP 211432</t>
-        </is>
-      </c>
-      <c r="C262" t="n">
-        <v>65.15000000000001</v>
-      </c>
+          <t>STEAM PURCHASE</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="n">
+        <v>98.27</v>
+      </c>
+      <c r="D262" s="2" t="n"/>
       <c r="E262" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -5150,17 +5666,19 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>UBER *TRIP 384882</t>
-        </is>
-      </c>
-      <c r="C263" t="n">
-        <v>45.11</v>
-      </c>
+          <t>SUPER-PHARM 9992</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="D263" s="2" t="n"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -5168,17 +5686,19 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>YANGO 208868</t>
-        </is>
-      </c>
-      <c r="C264" t="n">
-        <v>35.41</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="n">
+        <v>152.79</v>
+      </c>
+      <c r="D264" s="2" t="n"/>
       <c r="E264" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -5186,89 +5706,99 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>YANGO 835230</t>
-        </is>
-      </c>
-      <c r="C265" t="n">
-        <v>38.98</v>
-      </c>
+          <t>UBER *TRIP 192402</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="D265" s="2" t="n"/>
       <c r="E265" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>45562</v>
+        <v>45561</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>ARCAFFE DIZENGOFF</t>
-        </is>
-      </c>
-      <c r="C266" t="n">
-        <v>40.2</v>
-      </c>
+          <t>UBER *TRIP 211432</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="n">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="D266" s="2" t="n"/>
       <c r="E266" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>45562</v>
+        <v>45561</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>EL AL AIRLINES 511602</t>
-        </is>
-      </c>
-      <c r="C267" t="n">
-        <v>2387.28</v>
-      </c>
+          <t>UBER *TRIP 384882</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="D267" s="2" t="n"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>45562</v>
+        <v>45561</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>FX COMMISSION 010032</t>
-        </is>
-      </c>
-      <c r="C268" t="n">
-        <v>37.68</v>
-      </c>
+          <t>YANGO 208868</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="n">
+        <v>35.41</v>
+      </c>
+      <c r="D268" s="2" t="n"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>45562</v>
+        <v>45561</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>INCOMING TRANSFER ACME DIGITAL LTD INV-1489</t>
-        </is>
-      </c>
-      <c r="D269" t="n">
-        <v>12294.45</v>
-      </c>
+          <t>YANGO 835230</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="n">
+        <v>38.98</v>
+      </c>
+      <c r="D269" s="2" t="n"/>
       <c r="E269" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -5276,17 +5806,19 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>INCOMING TRANSFER ACME DIGITAL LTD INV-7572</t>
-        </is>
-      </c>
-      <c r="D270" t="n">
-        <v>14345.9</v>
-      </c>
+          <t>ARCAFFE DIZENGOFF</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="D270" s="2" t="n"/>
       <c r="E270" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -5294,17 +5826,19 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PAYPAL *UDEMY</t>
-        </is>
-      </c>
-      <c r="C271" t="n">
-        <v>87.11</v>
-      </c>
+          <t>EL AL AIRLINES 511602</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="n">
+        <v>2387.28</v>
+      </c>
+      <c r="D271" s="2" t="n"/>
       <c r="E271" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -5312,17 +5846,19 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>RAMI LEVY</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>311.99</v>
-      </c>
+          <t>FX COMMISSION 010032</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="n">
+        <v>37.68</v>
+      </c>
+      <c r="D272" s="2" t="n"/>
       <c r="E272" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -5330,17 +5866,19 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>208.41</v>
+          <t>INCOMING TRANSFER ACME DIGITAL LTD INV-1489</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="n"/>
+      <c r="D273" s="2" t="n">
+        <v>12294.45</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -5348,17 +5886,19 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>WOLT IL 644701</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>127.53</v>
+          <t>INCOMING TRANSFER ACME DIGITAL LTD INV-7572</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="n"/>
+      <c r="D274" s="2" t="n">
+        <v>14345.9</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F274" s="2" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -5366,89 +5906,99 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>YANGO 547224</t>
-        </is>
-      </c>
-      <c r="C275" t="n">
-        <v>76.05</v>
-      </c>
+          <t>PAYPAL *UDEMY</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="n">
+        <v>87.11</v>
+      </c>
+      <c r="D275" s="2" t="n"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>45563</v>
+        <v>45562</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>19.88</v>
-      </c>
+          <t>RAMI LEVY</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="n">
+        <v>311.99</v>
+      </c>
+      <c r="D276" s="2" t="n"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>45563</v>
+        <v>45562</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>EL AL AIRLINES 913354</t>
-        </is>
-      </c>
-      <c r="C277" t="n">
-        <v>1707.98</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="n">
+        <v>208.41</v>
+      </c>
+      <c r="D277" s="2" t="n"/>
       <c r="E277" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>45563</v>
+        <v>45562</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 02196</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>144.45</v>
-      </c>
+          <t>WOLT IL 644701</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="n">
+        <v>127.53</v>
+      </c>
+      <c r="D278" s="2" t="n"/>
       <c r="E278" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F278" s="2" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>45563</v>
+        <v>45562</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>MISHKENOT REVIVIM 23526</t>
-        </is>
-      </c>
-      <c r="C279" t="n">
-        <v>201.94</v>
-      </c>
+          <t>YANGO 547224</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="n">
+        <v>76.05</v>
+      </c>
+      <c r="D279" s="2" t="n"/>
       <c r="E279" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F279" s="2" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -5456,17 +6006,19 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PAYPAL *ENVATO</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>22.49</v>
-      </c>
+          <t>APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="D280" s="2" t="n"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -5474,17 +6026,19 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>RAMI LEVY</t>
-        </is>
-      </c>
-      <c r="C281" t="n">
-        <v>188.3</v>
-      </c>
+          <t>EL AL AIRLINES 913354</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="n">
+        <v>1707.98</v>
+      </c>
+      <c r="D281" s="2" t="n"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F281" s="2" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -5492,17 +6046,19 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>SHUFERSAL DEAL 8093</t>
-        </is>
-      </c>
-      <c r="C282" t="n">
-        <v>212.98</v>
-      </c>
+          <t>MISHKENOT REVIVIM 02196</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="n">
+        <v>144.45</v>
+      </c>
+      <c r="D282" s="2" t="n"/>
       <c r="E282" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F282" s="2" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -5510,17 +6066,19 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C283" t="n">
-        <v>181.64</v>
-      </c>
+          <t>MISHKENOT REVIVIM 23526</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="n">
+        <v>201.94</v>
+      </c>
+      <c r="D283" s="2" t="n"/>
       <c r="E283" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F283" s="2" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -5528,17 +6086,19 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>TENBIS LTD</t>
-        </is>
-      </c>
-      <c r="C284" t="n">
-        <v>69.20999999999999</v>
-      </c>
+          <t>PAYPAL *ENVATO</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="D284" s="2" t="n"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -5546,89 +6106,99 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>WOLT IL 042839</t>
-        </is>
-      </c>
-      <c r="C285" t="n">
-        <v>139.31</v>
-      </c>
+          <t>RAMI LEVY</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="n">
+        <v>188.3</v>
+      </c>
+      <c r="D285" s="2" t="n"/>
       <c r="E285" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>45564</v>
+        <v>45563</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>BOOKING.COM 97286520</t>
-        </is>
-      </c>
-      <c r="C286" t="n">
-        <v>331.1</v>
-      </c>
+          <t>SHUFERSAL DEAL 8093</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="n">
+        <v>212.98</v>
+      </c>
+      <c r="D286" s="2" t="n"/>
       <c r="E286" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>45564</v>
+        <v>45563</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>GETT TAXI 648084</t>
-        </is>
-      </c>
-      <c r="C287" t="n">
-        <v>58.75</v>
-      </c>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="n">
+        <v>181.64</v>
+      </c>
+      <c r="D287" s="2" t="n"/>
       <c r="E287" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F287" s="2" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>45564</v>
+        <v>45563</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>INCOME TAX ADVANCE PAYMENT</t>
-        </is>
-      </c>
-      <c r="C288" t="n">
-        <v>3467.59</v>
-      </c>
+          <t>TENBIS LTD</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="n">
+        <v>69.20999999999999</v>
+      </c>
+      <c r="D288" s="2" t="n"/>
       <c r="E288" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>45564</v>
+        <v>45563</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ORNA PRINT &amp; DESIGN</t>
-        </is>
-      </c>
-      <c r="C289" t="n">
-        <v>180.92</v>
-      </c>
+          <t>WOLT IL 042839</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="n">
+        <v>139.31</v>
+      </c>
+      <c r="D289" s="2" t="n"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F289" s="2" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -5636,17 +6206,19 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PAYPAL *UDEMY</t>
-        </is>
-      </c>
-      <c r="C290" t="n">
-        <v>78.53</v>
-      </c>
+          <t>BOOKING.COM 97286520</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="n">
+        <v>331.1</v>
+      </c>
+      <c r="D290" s="2" t="n"/>
       <c r="E290" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -5654,71 +6226,79 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>RAMI LEVY</t>
-        </is>
-      </c>
-      <c r="C291" t="n">
-        <v>193.32</v>
-      </c>
+          <t>INCOME TAX ADVANCE PAYMENT</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="n">
+        <v>3467.59</v>
+      </c>
+      <c r="D291" s="2" t="n"/>
       <c r="E291" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F291" s="2" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>45565</v>
+        <v>45564</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>APPLE.COM/BILL</t>
-        </is>
-      </c>
-      <c r="C292" t="n">
-        <v>30.84</v>
-      </c>
+          <t>ORNA PRINT &amp; DESIGN</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="n">
+        <v>180.92</v>
+      </c>
+      <c r="D292" s="2" t="n"/>
       <c r="E292" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>45565</v>
+        <v>45564</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>BITUACH LEUMI NATIONAL INSURANCE</t>
-        </is>
-      </c>
-      <c r="C293" t="n">
-        <v>1120</v>
-      </c>
+          <t>PAYPAL *UDEMY</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="n">
+        <v>78.53</v>
+      </c>
+      <c r="D293" s="2" t="n"/>
       <c r="E293" t="inlineStr">
         <is>
-          <t>ILS</t>
-        </is>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>45565</v>
+        <v>45564</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>CAFE NIMROD</t>
-        </is>
-      </c>
-      <c r="C294" t="n">
-        <v>19.64</v>
-      </c>
+          <t>RAMI LEVY</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="n">
+        <v>193.32</v>
+      </c>
+      <c r="D294" s="2" t="n"/>
       <c r="E294" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -5726,17 +6306,19 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>CAFE NIMROD</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
-        <v>44.43</v>
-      </c>
+          <t>APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="n">
+        <v>30.84</v>
+      </c>
+      <c r="D295" s="2" t="n"/>
       <c r="E295" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F295" s="2" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -5744,17 +6326,19 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>RAMI LEVY</t>
-        </is>
-      </c>
-      <c r="C296" t="n">
-        <v>342.52</v>
-      </c>
+          <t>BITUACH LEUMI NATIONAL INSURANCE</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="n">
+        <v>1120</v>
+      </c>
+      <c r="D296" s="2" t="n"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F296" s="2" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -5762,17 +6346,19 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>SUPER-PHARM 3766</t>
-        </is>
-      </c>
-      <c r="C297" t="n">
-        <v>174.55</v>
-      </c>
+          <t>CAFE NIMROD</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="D297" s="2" t="n"/>
       <c r="E297" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F297" s="2" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -5780,17 +6366,19 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>SUSHI BAR ROTHSCHILD</t>
-        </is>
-      </c>
-      <c r="C298" t="n">
-        <v>205.42</v>
-      </c>
+          <t>CAFE NIMROD</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="D298" s="2" t="n"/>
       <c r="E298" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -5798,17 +6386,19 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>TENBIS LTD</t>
-        </is>
-      </c>
-      <c r="C299" t="n">
-        <v>48.46</v>
-      </c>
+          <t>RAMI LEVY</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="n">
+        <v>342.52</v>
+      </c>
+      <c r="D299" s="2" t="n"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -5816,17 +6406,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>UBER *TRIP 061492</t>
-        </is>
-      </c>
-      <c r="C300" t="n">
-        <v>63.43</v>
-      </c>
+          <t>SUPER-PHARM 3766</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="n">
+        <v>174.55</v>
+      </c>
+      <c r="D300" s="2" t="n"/>
       <c r="E300" t="inlineStr">
         <is>
           <t>ILS</t>
         </is>
       </c>
+      <c r="F300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -5834,17 +6426,119 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
+          <t>SUSHI BAR ROTHSCHILD</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="n">
+        <v>205.42</v>
+      </c>
+      <c r="D301" s="2" t="n"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>TENBIS LTD</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="D302" s="2" t="n"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>UBER *TRIP 061492</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="D303" s="2" t="n"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
           <t>WOLT IL 349486</t>
         </is>
       </c>
-      <c r="C301" t="n">
+      <c r="C304" s="2" t="n">
         <v>129.02</v>
       </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>ILS</t>
-        </is>
-      </c>
+      <c r="D304" s="2" t="n"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Closing balance</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="n"/>
+      <c r="D305" s="2" t="n"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="n">
+        <v>120657.37</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>TOTAL ILS</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="n">
+        <v>63797.49</v>
+      </c>
+      <c r="D306" s="2" t="n">
+        <v>172004.56</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>ILS</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
